--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486736_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486736_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6232</v>
+        <v>5.8705</v>
       </c>
       <c r="E2" t="n">
-        <v>6.423</v>
+        <v>4.72</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2002</v>
+        <v>1.1505</v>
       </c>
       <c r="G2" t="n">
         <v>5.5877</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0008</v>
+        <v>1.2482</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6197</v>
+        <v>0.9167</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3812</v>
+        <v>0.3315</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1943</v>
+        <v>5.5502</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3747</v>
+        <v>5.5816</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1804</v>
+        <v>-0.0314</v>
       </c>
       <c r="G3" t="n">
         <v>3.9187</v>
@@ -688,13 +688,13 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0166</v>
+        <v>0.3724</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1928</v>
+        <v>0.3997</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1762</v>
+        <v>-0.0272</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2856</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8714</v>
+        <v>4.5541</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5412</v>
+        <v>3.5964</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3302</v>
+        <v>0.9577</v>
       </c>
       <c r="G4" t="n">
         <v>1.6931</v>
@@ -766,13 +766,13 @@
         <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5725</v>
+        <v>1.2552</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3032</v>
+        <v>0.3584</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2692</v>
+        <v>0.8968</v>
       </c>
       <c r="V4" t="n">
         <v>1.7989</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>J. DEL CASTILLO LEON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9631</v>
+        <v>4.4713</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2492</v>
+        <v>3.693</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2861</v>
+        <v>0.7783</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5385</v>
+        <v>4.5263</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0553</v>
+        <v>1.635</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5938</v>
+        <v>2.8913</v>
       </c>
       <c r="J5" t="n">
-        <v>2.608</v>
+        <v>5.5826</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6067</v>
+        <v>1.6355</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2147</v>
+        <v>3.9471</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0695</v>
+        <v>-1.0563</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5514</v>
+        <v>-0.0005</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6209</v>
+        <v>-1.0558</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7723</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4247</v>
+        <v>0.2965</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4136</v>
+        <v>0.3927</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0111</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2277</v>
+        <v>0.6138</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2277</v>
+        <v>0.6138</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. DEL CASTILLO LEON</t>
+          <t>A. ROSALES DARIAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.8879</v>
+        <v>4.3036</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3828</v>
+        <v>3.4178</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5051</v>
+        <v>0.8858</v>
       </c>
       <c r="G6" t="n">
-        <v>4.5263</v>
+        <v>0.1616</v>
       </c>
       <c r="H6" t="n">
-        <v>1.635</v>
+        <v>1.3033</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8913</v>
+        <v>-1.1417</v>
       </c>
       <c r="J6" t="n">
-        <v>5.5826</v>
+        <v>1.5558</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6355</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>3.9471</v>
+        <v>0.7347</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0563</v>
+        <v>-1.3942</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0005</v>
+        <v>0.4822</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0558</v>
+        <v>-1.8764</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2869</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0825</v>
+        <v>0.0205</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3694</v>
+        <v>0.8279</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6138</v>
+        <v>1.5559</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6138</v>
+        <v>1.8415</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ROSALES DARIAS</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6761</v>
+        <v>4.035</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7903</v>
+        <v>4.0976</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8858</v>
+        <v>-0.0626</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1616</v>
+        <v>1.5385</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3033</v>
+        <v>-0.0553</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1417</v>
+        <v>1.5938</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5558</v>
+        <v>2.608</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8211000000000001</v>
+        <v>-0.6067</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7347</v>
+        <v>3.2147</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3942</v>
+        <v>-1.0695</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4822</v>
+        <v>0.5514</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8764</v>
+        <v>-1.6209</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2208</v>
+        <v>0.4965</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.607</v>
+        <v>0.2619</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8279</v>
+        <v>0.2346</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5559</v>
+        <v>1.2277</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8415</v>
+        <v>1.2277</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. AMANDIO</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2119</v>
+        <v>3.4553</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8264</v>
+        <v>1.1459</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3855</v>
+        <v>2.3093</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0944</v>
+        <v>-1.1267</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.103</v>
+        <v>1.0074</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1974</v>
+        <v>-2.1341</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1365</v>
+        <v>-0.5533</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9991</v>
+        <v>-0.0265</v>
       </c>
       <c r="L8" t="n">
-        <v>3.1356</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0421</v>
+        <v>-0.5734</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8961</v>
+        <v>1.034</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9382</v>
+        <v>-1.6074</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5446</v>
+        <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2414</v>
+        <v>0.9448</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3584</v>
+        <v>0.1859</v>
       </c>
       <c r="U8" t="n">
-        <v>0.883</v>
+        <v>0.7589</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2277</v>
+        <v>1.5133</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2277</v>
+        <v>1.5133</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>E. AMANDIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.1173</v>
+        <v>3.1429</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9322</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1852</v>
+        <v>2.2613</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1267</v>
+        <v>2.0944</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0074</v>
+        <v>-0.103</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1341</v>
+        <v>2.1974</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5533</v>
+        <v>2.1365</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0265</v>
+        <v>-0.9991</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5266999999999999</v>
+        <v>3.1356</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5734</v>
+        <v>-0.0421</v>
       </c>
       <c r="N9" t="n">
-        <v>1.034</v>
+        <v>0.8961</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6074</v>
+        <v>-0.9382</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1239</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6068</v>
+        <v>1.1724</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0279</v>
+        <v>0.4136</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6347</v>
+        <v>0.7588</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5133</v>
+        <v>1.2277</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5133</v>
+        <v>1.2277</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.3235</v>
+        <v>2.6477</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3989</v>
+        <v>0.3506</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9246</v>
+        <v>2.2971</v>
       </c>
       <c r="G10" t="n">
         <v>0.7845</v>
@@ -1234,13 +1234,13 @@
         <v>1.5446</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3033</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1928</v>
+        <v>0.1446</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1104</v>
+        <v>0.4829</v>
       </c>
       <c r="V10" t="n">
         <v>0.6565</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8715</v>
+        <v>2.5707</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4959</v>
+        <v>3.2199</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6244</v>
+        <v>-0.6492</v>
       </c>
       <c r="G11" t="n">
         <v>-0.322</v>
@@ -1312,13 +1312,13 @@
         <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5128</v>
+        <v>0.1863</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4966</v>
+        <v>0.2273</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0162</v>
+        <v>-0.041</v>
       </c>
       <c r="V11" t="n">
         <v>2.1271</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4314</v>
+        <v>-1.7405</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8566</v>
+        <v>-0.5945</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5748</v>
+        <v>-1.1459</v>
       </c>
       <c r="G12" t="n">
         <v>-2.201</v>
@@ -1390,13 +1390,13 @@
         <v>1.9308</v>
       </c>
       <c r="S12" t="n">
-        <v>0.723</v>
+        <v>0.4139</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1383</v>
+        <v>0.1238</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8613</v>
+        <v>0.2901</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8842</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>38.30880000000001</v>
+        <v>38.8608</v>
       </c>
       <c r="E13" t="n">
-        <v>29.558</v>
+        <v>30.1099</v>
       </c>
       <c r="F13" t="n">
-        <v>8.750900000000001</v>
+        <v>8.7509</v>
       </c>
       <c r="G13" t="n">
         <v>16.6551</v>
@@ -1468,13 +1468,13 @@
         <v>18.3424</v>
       </c>
       <c r="S13" t="n">
-        <v>7.310199999999999</v>
+        <v>7.861999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8932</v>
+        <v>3.4451</v>
       </c>
       <c r="U13" t="n">
-        <v>4.417</v>
+        <v>4.4171</v>
       </c>
       <c r="V13" t="n">
         <v>8.5511</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5026</v>
+        <v>5.0322</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7299</v>
+        <v>5.9367</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2273</v>
+        <v>-0.9045</v>
       </c>
       <c r="G14" t="n">
         <v>7.1507</v>
@@ -1546,13 +1546,13 @@
         <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2193</v>
+        <v>-0.6896</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8554</v>
+        <v>-0.6485</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3639</v>
+        <v>-0.0411</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6565</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0435</v>
+        <v>-1.3467</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6254</v>
+        <v>1.6946</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.6689</v>
+        <v>-3.0414</v>
       </c>
       <c r="G15" t="n">
         <v>-1.2099</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3515</v>
+        <v>0.0482</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1302</v>
+        <v>0.1994</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2213</v>
+        <v>-0.1512</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5712</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6413</v>
+        <v>-1.7654</v>
       </c>
       <c r="E16" t="n">
         <v>0.8139</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4552</v>
+        <v>-2.5793</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1144</v>
@@ -1702,13 +1702,13 @@
         <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2759</v>
+        <v>-0.4</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2487</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0271</v>
+        <v>-0.1513</v>
       </c>
       <c r="V16" t="n">
         <v>0.3282</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.5937</v>
+        <v>-2.1137</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4873</v>
+        <v>1.6941</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.081</v>
+        <v>-3.8079</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1823</v>
@@ -1780,13 +1780,13 @@
         <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.2483</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6347</v>
+        <v>-0.4278</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.09370000000000001</v>
+        <v>0.1795</v>
       </c>
       <c r="V17" t="n">
         <v>-2.4554</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.3984</v>
+        <v>-4.4937</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.0721</v>
+        <v>-2.9687</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3263</v>
+        <v>-1.525</v>
       </c>
       <c r="G18" t="n">
         <v>-3.5694</v>
@@ -1858,13 +1858,13 @@
         <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7944</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9933</v>
+        <v>-0.8899</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1989</v>
+        <v>0.0002</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6138</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. CARRON GRILLO</t>
+          <t>J. MOLINA MELENDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.0164</v>
+        <v>-4.6579</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.6777</v>
+        <v>1.1671</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3386</v>
+        <v>-5.8249</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.0991</v>
+        <v>-2.2898</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.0276</v>
+        <v>-1.4693</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0715</v>
+        <v>-0.8205</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.9327</v>
+        <v>3.0841</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.7165</v>
+        <v>0.6696</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2162</v>
+        <v>2.4146</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1664</v>
+        <v>-5.3739</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.311</v>
+        <v>-2.1389</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1447</v>
+        <v>-3.2351</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.0892</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6896</v>
+        <v>-1.5378</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.745</v>
+        <v>-0.6694</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0554</v>
+        <v>-0.8685</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MOLINA MELENDEZ</t>
+          <t>H. CARRON GRILLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.1998</v>
+        <v>-4.913</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6499</v>
+        <v>-4.5743</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.8498</v>
+        <v>-0.3386</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2898</v>
+        <v>-5.0991</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4693</v>
+        <v>-4.0276</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8205</v>
+        <v>-1.0715</v>
       </c>
       <c r="J20" t="n">
-        <v>3.0841</v>
+        <v>-3.9327</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6696</v>
+        <v>-2.7165</v>
       </c>
       <c r="L20" t="n">
-        <v>2.4146</v>
+        <v>-1.2162</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.3739</v>
+        <v>-1.1664</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.1389</v>
+        <v>-1.311</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.2351</v>
+        <v>0.1447</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0892</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0798</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1865</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8933</v>
+        <v>0.0554</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.1182</v>
+        <v>-10.1472</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5253</v>
+        <v>-4.6287</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.593</v>
+        <v>-5.5185</v>
       </c>
       <c r="G21" t="n">
         <v>-7.1401</v>
@@ -2092,13 +2092,13 @@
         <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5227</v>
+        <v>-1.5517</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3866</v>
+        <v>-0.4901</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1361</v>
+        <v>-1.0616</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8415</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-13.8002</v>
+        <v>-13.9036</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.7822</v>
+        <v>-7.8856</v>
       </c>
       <c r="F22" t="n">
         <v>-6.0181</v>
@@ -2170,10 +2170,10 @@
         <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3517</v>
+        <v>-1.4551</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.497</v>
+        <v>-0.6004</v>
       </c>
       <c r="U22" t="n">
         <v>-0.8547</v>
@@ -2203,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-38.30889999999999</v>
+        <v>-38.309</v>
       </c>
       <c r="E23" t="n">
         <v>-8.7509</v>
@@ -2224,7 +2224,7 @@
         <v>12.2523</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.408800000000001</v>
+        <v>-2.4088</v>
       </c>
       <c r="L23" t="n">
         <v>14.6612</v>
@@ -2248,13 +2248,13 @@
         <v>12.55</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.3102</v>
+        <v>-7.3101</v>
       </c>
       <c r="T23" t="n">
         <v>-4.417</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.8932</v>
+        <v>-2.8933</v>
       </c>
       <c r="V23" t="n">
         <v>-8.5512</v>
